--- a/swimmers.xlsx
+++ b/swimmers.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3530" uniqueCount="1824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3815" uniqueCount="1965">
   <si>
     <t>대회날짜</t>
   </si>
@@ -5498,6 +5498,433 @@
     <t>2시간 10분 5050m</t>
   </si>
   <si>
+    <t>희망종목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-16 20:33:31</t>
+  </si>
+  <si>
+    <t>이정욱</t>
+  </si>
+  <si>
+    <t>01043444300</t>
+  </si>
+  <si>
+    <t>4300</t>
+  </si>
+  <si>
+    <t>860218-1528518</t>
+  </si>
+  <si>
+    <t>김유리</t>
+  </si>
+  <si>
+    <t>01043274566</t>
+  </si>
+  <si>
+    <t>2026-10-16 21:52:27</t>
+  </si>
+  <si>
+    <t>정웅태</t>
+  </si>
+  <si>
+    <t>01053383766</t>
+  </si>
+  <si>
+    <t>3766</t>
+  </si>
+  <si>
+    <t>750225-1475742</t>
+  </si>
+  <si>
+    <t>박혜정</t>
+  </si>
+  <si>
+    <t>01032365934</t>
+  </si>
+  <si>
+    <t>2026-10-16 22:00:04</t>
+  </si>
+  <si>
+    <t>김현중</t>
+  </si>
+  <si>
+    <t>010-9581-0940</t>
+  </si>
+  <si>
+    <t>0940</t>
+  </si>
+  <si>
+    <t>830130-1244721</t>
+  </si>
+  <si>
+    <t>김중혁</t>
+  </si>
+  <si>
+    <t>010-8887-8049</t>
+  </si>
+  <si>
+    <t>1:45</t>
+  </si>
+  <si>
+    <t>2026-10-16 22:27:38</t>
+  </si>
+  <si>
+    <t>한상윤</t>
+  </si>
+  <si>
+    <t>010.9915.1979</t>
+  </si>
+  <si>
+    <t>1979</t>
+  </si>
+  <si>
+    <t>KBS 물텀벙</t>
+  </si>
+  <si>
+    <t>720524-1056711</t>
+  </si>
+  <si>
+    <t>한유담</t>
+  </si>
+  <si>
+    <t>010.3085.0135</t>
+  </si>
+  <si>
+    <t>2시간9분</t>
+  </si>
+  <si>
+    <t>2026-10-16 22:53:42</t>
+  </si>
+  <si>
+    <t>김소운</t>
+  </si>
+  <si>
+    <t>01084023975</t>
+  </si>
+  <si>
+    <t>3975</t>
+  </si>
+  <si>
+    <t>980422-2200613</t>
+  </si>
+  <si>
+    <t>홍성찬</t>
+  </si>
+  <si>
+    <t>01081938933</t>
+  </si>
+  <si>
+    <t>1:20분</t>
+  </si>
+  <si>
+    <t>2026-10-17 00:10:16 (수정)</t>
+  </si>
+  <si>
+    <t>임준혁</t>
+  </si>
+  <si>
+    <t>01096409134</t>
+  </si>
+  <si>
+    <t>9134</t>
+  </si>
+  <si>
+    <t>있음 시 기타 사항에 정확히 기재|올라운더</t>
+  </si>
+  <si>
+    <t>011109-3933211</t>
+  </si>
+  <si>
+    <t>임기식</t>
+  </si>
+  <si>
+    <t>010-2689-2317</t>
+  </si>
+  <si>
+    <t>1:15</t>
+  </si>
+  <si>
+    <t>2026-10-17 09:34:54 (수정)</t>
+  </si>
+  <si>
+    <t>최준국</t>
+  </si>
+  <si>
+    <t>010-9342-3103</t>
+  </si>
+  <si>
+    <t>3103</t>
+  </si>
+  <si>
+    <t>820818-1473514</t>
+  </si>
+  <si>
+    <t>김수진</t>
+  </si>
+  <si>
+    <t>010-6383-2933</t>
+  </si>
+  <si>
+    <t>'26년 울트라수영 8.5km 4시간 7분(4시간 초과) / 주관 협회에서 컷 오프 이후 시간을 배려해 주신다면 완영 하고 싶습니다.</t>
+  </si>
+  <si>
+    <t>2026-10-17 05:10:48</t>
+  </si>
+  <si>
+    <t>김진석</t>
+  </si>
+  <si>
+    <t>010-9775-5934</t>
+  </si>
+  <si>
+    <t>5934</t>
+  </si>
+  <si>
+    <t>800226-1085211</t>
+  </si>
+  <si>
+    <t>이지영</t>
+  </si>
+  <si>
+    <t>010-7445-8634</t>
+  </si>
+  <si>
+    <t>2026-10-17 06:02:30</t>
+  </si>
+  <si>
+    <t>신승철</t>
+  </si>
+  <si>
+    <t>010-4900-7091</t>
+  </si>
+  <si>
+    <t>7091</t>
+  </si>
+  <si>
+    <t>850516-1110111</t>
+  </si>
+  <si>
+    <t>김말희</t>
+  </si>
+  <si>
+    <t>010-6740-5040</t>
+  </si>
+  <si>
+    <t>2026-10-17 07:45:46</t>
+  </si>
+  <si>
+    <t>김태영</t>
+  </si>
+  <si>
+    <t>010-6739-5632</t>
+  </si>
+  <si>
+    <t>5632</t>
+  </si>
+  <si>
+    <t>TEAM W.S.M</t>
+  </si>
+  <si>
+    <t>910124-2122020</t>
+  </si>
+  <si>
+    <t>조은일</t>
+  </si>
+  <si>
+    <t>010-2665-8590</t>
+  </si>
+  <si>
+    <t>2026-10-17 08:36:33</t>
+  </si>
+  <si>
+    <t>01026658590</t>
+  </si>
+  <si>
+    <t>8590</t>
+  </si>
+  <si>
+    <t>911104-1120815</t>
+  </si>
+  <si>
+    <t>01067395632</t>
+  </si>
+  <si>
+    <t>2026-10-17 08:39:36</t>
+  </si>
+  <si>
+    <t>박희환</t>
+  </si>
+  <si>
+    <t>01089928396</t>
+  </si>
+  <si>
+    <t>8396</t>
+  </si>
+  <si>
+    <t>641212-1000315</t>
+  </si>
+  <si>
+    <t>김순덕</t>
+  </si>
+  <si>
+    <t>01052178396</t>
+  </si>
+  <si>
+    <t>부천 3.5Km 1시간15분</t>
+  </si>
+  <si>
+    <t>2026-10-17 09:40:24</t>
+  </si>
+  <si>
+    <t>권민숙</t>
+  </si>
+  <si>
+    <t>010-3842-3757</t>
+  </si>
+  <si>
+    <t>3757</t>
+  </si>
+  <si>
+    <t>770624-2351714</t>
+  </si>
+  <si>
+    <t>장원석</t>
+  </si>
+  <si>
+    <t>010-9177-2066</t>
+  </si>
+  <si>
+    <t>1시간 57분</t>
+  </si>
+  <si>
+    <t>있음 시 기타 사항에 정확히 기재|목동철인</t>
+  </si>
+  <si>
+    <t>2026-10-17 10:50:33 (수정)</t>
+  </si>
+  <si>
+    <t>김령희</t>
+  </si>
+  <si>
+    <t>01081209239</t>
+  </si>
+  <si>
+    <t>970110-2057819</t>
+  </si>
+  <si>
+    <t>박경규</t>
+  </si>
+  <si>
+    <t>01098831192</t>
+  </si>
+  <si>
+    <t>2026-10-17 12:58:28</t>
+  </si>
+  <si>
+    <t>김시현</t>
+  </si>
+  <si>
+    <t>01041868848</t>
+  </si>
+  <si>
+    <t>있음 시 기타 사항에 정확히 기재|세종철인클럽</t>
+  </si>
+  <si>
+    <t>680320~1450720</t>
+  </si>
+  <si>
+    <t>김조은</t>
+  </si>
+  <si>
+    <t>01041333113</t>
+  </si>
+  <si>
+    <t>2026-10-17 13:57:02 (수정)</t>
+  </si>
+  <si>
+    <t>조남혁</t>
+  </si>
+  <si>
+    <t>010-7293-9116</t>
+  </si>
+  <si>
+    <t>9116</t>
+  </si>
+  <si>
+    <t>있음 시 기타 사항에 정확히 기재|TEAM WSM</t>
+  </si>
+  <si>
+    <t>830930-1046132</t>
+  </si>
+  <si>
+    <t>조세구</t>
+  </si>
+  <si>
+    <t>010-4230-3368</t>
+  </si>
+  <si>
+    <t>2026-10-17 14:29:54 (수정)</t>
+  </si>
+  <si>
+    <t>허원영</t>
+  </si>
+  <si>
+    <t>010-9840-0615</t>
+  </si>
+  <si>
+    <t>0615</t>
+  </si>
+  <si>
+    <t>801227-1148211</t>
+  </si>
+  <si>
+    <t>최시영</t>
+  </si>
+  <si>
+    <t>010-5456-1981</t>
+  </si>
+  <si>
+    <t>2026-10-17 15:31:02 (수정)</t>
+  </si>
+  <si>
+    <t>이경환</t>
+  </si>
+  <si>
+    <t>01037793851</t>
+  </si>
+  <si>
+    <t>841123-1161718</t>
+  </si>
+  <si>
+    <t>양정윤</t>
+  </si>
+  <si>
+    <t>010.6333.3018</t>
+  </si>
+  <si>
+    <t>2026-10-17 16:17:05</t>
+  </si>
+  <si>
+    <t>강연화</t>
+  </si>
+  <si>
+    <t>01027021813</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>811227-2644019</t>
+  </si>
+  <si>
+    <t>박종환</t>
+  </si>
+  <si>
+    <t>01077574574</t>
+  </si>
+  <si>
     <t>납부완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5506,15 +5933,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이전 대회 참가권 획득</t>
+    <t>무료출전권 획득</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10/23일 확인예정 입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>희망종목</t>
+    <t>10/19일 19시 이후 확인 예정입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5583,36 +6006,40 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="21" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="21" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1"/>
+    <cellStyle name="표준 4" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5904,9 +6331,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG232"/>
+  <dimension ref="A1:AG251"/>
   <sheetFormatPr defaultRowHeight="17.25"/>
   <cols>
+    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5960,7 +6388,7 @@
         <v>14</v>
       </c>
       <c r="Q1" t="s">
-        <v>1823</v>
+        <v>1819</v>
       </c>
       <c r="R1" t="s">
         <v>15</v>
@@ -6129,7 +6557,7 @@
         <v>73</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>74</v>
@@ -6203,7 +6631,7 @@
         <v>79</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>80</v>
@@ -6277,7 +6705,7 @@
         <v>89</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>90</v>
@@ -6351,7 +6779,7 @@
         <v>97</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>98</v>
@@ -6425,7 +6853,7 @@
         <v>106</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>107</v>
@@ -6499,7 +6927,7 @@
         <v>114</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>115</v>
@@ -6573,7 +7001,7 @@
         <v>123</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>124</v>
@@ -6647,7 +7075,7 @@
         <v>132</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>133</v>
@@ -6721,7 +7149,7 @@
         <v>140</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>141</v>
@@ -6795,7 +7223,7 @@
         <v>148</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>149</v>
@@ -6869,7 +7297,7 @@
         <v>157</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>158</v>
@@ -6943,7 +7371,7 @@
         <v>166</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>167</v>
@@ -7017,7 +7445,7 @@
         <v>175</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>176</v>
@@ -7091,7 +7519,7 @@
         <v>186</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>187</v>
@@ -7165,7 +7593,7 @@
         <v>195</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>196</v>
@@ -7239,7 +7667,7 @@
         <v>204</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>205</v>
@@ -7313,7 +7741,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>212</v>
@@ -7387,7 +7815,7 @@
         <v>219</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>220</v>
@@ -7461,7 +7889,7 @@
         <v>227</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>228</v>
@@ -7535,7 +7963,7 @@
         <v>234</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>235</v>
@@ -7609,7 +8037,7 @@
         <v>242</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>243</v>
@@ -7683,7 +8111,7 @@
         <v>249</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>250</v>
@@ -7757,7 +8185,7 @@
         <v>256</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>257</v>
@@ -7831,7 +8259,7 @@
         <v>263</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>264</v>
@@ -7905,7 +8333,7 @@
         <v>271</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>272</v>
@@ -7979,7 +8407,7 @@
         <v>278</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>279</v>
@@ -8053,7 +8481,7 @@
         <v>285</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>286</v>
@@ -8127,7 +8555,7 @@
         <v>293</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>294</v>
@@ -8201,7 +8629,7 @@
         <v>301</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>302</v>
@@ -8275,7 +8703,7 @@
         <v>308</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>309</v>
@@ -8349,7 +8777,7 @@
         <v>317</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>318</v>
@@ -8423,7 +8851,7 @@
         <v>325</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>326</v>
@@ -8497,7 +8925,7 @@
         <v>332</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>333</v>
@@ -8571,7 +8999,7 @@
         <v>340</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>341</v>
@@ -8645,7 +9073,7 @@
         <v>347</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>348</v>
@@ -8719,7 +9147,7 @@
         <v>354</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>355</v>
@@ -8793,7 +9221,7 @@
         <v>361</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>362</v>
@@ -8867,7 +9295,7 @@
         <v>370</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>371</v>
@@ -8941,7 +9369,7 @@
         <v>378</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>379</v>
@@ -9015,7 +9443,7 @@
         <v>386</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>387</v>
@@ -9089,7 +9517,7 @@
         <v>394</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>395</v>
@@ -9163,7 +9591,7 @@
         <v>401</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>402</v>
@@ -9237,7 +9665,7 @@
         <v>409</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>410</v>
@@ -9311,7 +9739,7 @@
         <v>416</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>417</v>
@@ -9385,7 +9813,7 @@
         <v>425</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>426</v>
@@ -9459,7 +9887,7 @@
         <v>433</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>434</v>
@@ -9533,7 +9961,7 @@
         <v>441</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>442</v>
@@ -9607,7 +10035,7 @@
         <v>447</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>448</v>
@@ -9681,7 +10109,7 @@
         <v>455</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>456</v>
@@ -9755,7 +10183,7 @@
         <v>462</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>463</v>
@@ -9829,7 +10257,7 @@
         <v>470</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>471</v>
@@ -9903,7 +10331,7 @@
         <v>478</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>479</v>
@@ -9977,7 +10405,7 @@
         <v>485</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>486</v>
@@ -10051,7 +10479,7 @@
         <v>493</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>494</v>
@@ -10125,7 +10553,7 @@
         <v>312</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>313</v>
@@ -10199,7 +10627,7 @@
         <v>505</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>506</v>
@@ -10273,7 +10701,7 @@
         <v>514</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>515</v>
@@ -10347,7 +10775,7 @@
         <v>522</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>523</v>
@@ -10421,7 +10849,7 @@
         <v>531</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>532</v>
@@ -10495,7 +10923,7 @@
         <v>539</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>540</v>
@@ -10569,7 +10997,7 @@
         <v>546</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>547</v>
@@ -10643,7 +11071,7 @@
         <v>554</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>555</v>
@@ -10717,7 +11145,7 @@
         <v>561</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>562</v>
@@ -10791,7 +11219,7 @@
         <v>569</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>570</v>
@@ -10865,7 +11293,7 @@
         <v>574</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>575</v>
@@ -10939,7 +11367,7 @@
         <v>583</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>584</v>
@@ -11013,7 +11441,7 @@
         <v>591</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>592</v>
@@ -11087,7 +11515,7 @@
         <v>598</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>599</v>
@@ -11161,7 +11589,7 @@
         <v>606</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>607</v>
@@ -11235,7 +11663,7 @@
         <v>615</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>616</v>
@@ -11309,7 +11737,7 @@
         <v>624</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>625</v>
@@ -11383,7 +11811,7 @@
         <v>631</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>632</v>
@@ -11457,7 +11885,7 @@
         <v>638</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>639</v>
@@ -11531,7 +11959,7 @@
         <v>646</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>647</v>
@@ -11605,7 +12033,7 @@
         <v>654</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>655</v>
@@ -11679,7 +12107,7 @@
         <v>663</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>664</v>
@@ -11753,7 +12181,7 @@
         <v>670</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>671</v>
@@ -11827,7 +12255,7 @@
         <v>679</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>680</v>
@@ -11901,7 +12329,7 @@
         <v>602</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>686</v>
@@ -11975,7 +12403,7 @@
         <v>691</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>692</v>
@@ -12049,7 +12477,7 @@
         <v>699</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>700</v>
@@ -12123,7 +12551,7 @@
         <v>707</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>708</v>
@@ -12197,7 +12625,7 @@
         <v>420</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>715</v>
@@ -12271,7 +12699,7 @@
         <v>719</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>720</v>
@@ -12345,7 +12773,7 @@
         <v>726</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>727</v>
@@ -12419,7 +12847,7 @@
         <v>734</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>735</v>
@@ -12493,7 +12921,7 @@
         <v>742</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>743</v>
@@ -12567,7 +12995,7 @@
         <v>750</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>751</v>
@@ -12641,7 +13069,7 @@
         <v>758</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>759</v>
@@ -12715,7 +13143,7 @@
         <v>765</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>766</v>
@@ -12789,7 +13217,7 @@
         <v>772</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>773</v>
@@ -12863,7 +13291,7 @@
         <v>779</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>780</v>
@@ -12937,7 +13365,7 @@
         <v>787</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>788</v>
@@ -13011,7 +13439,7 @@
         <v>794</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>795</v>
@@ -13085,7 +13513,7 @@
         <v>802</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>803</v>
@@ -13159,7 +13587,7 @@
         <v>809</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>810</v>
@@ -13233,7 +13661,7 @@
         <v>816</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>817</v>
@@ -13307,7 +13735,7 @@
         <v>109</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>824</v>
@@ -13381,7 +13809,7 @@
         <v>829</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>830</v>
@@ -13455,7 +13883,7 @@
         <v>837</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>838</v>
@@ -13529,7 +13957,7 @@
         <v>845</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>846</v>
@@ -13603,7 +14031,7 @@
         <v>853</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>854</v>
@@ -13677,7 +14105,7 @@
         <v>861</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>862</v>
@@ -13751,7 +14179,7 @@
         <v>868</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>869</v>
@@ -13825,7 +14253,7 @@
         <v>517</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J107" s="1" t="s">
         <v>876</v>
@@ -13899,7 +14327,7 @@
         <v>881</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>882</v>
@@ -13973,7 +14401,7 @@
         <v>889</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>890</v>
@@ -14047,7 +14475,7 @@
         <v>896</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>897</v>
@@ -14121,7 +14549,7 @@
         <v>902</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J111" s="1" t="s">
         <v>903</v>
@@ -14195,7 +14623,7 @@
         <v>911</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>912</v>
@@ -14269,7 +14697,7 @@
         <v>918</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>1821</v>
+        <v>1963</v>
       </c>
       <c r="J113" s="1" t="s">
         <v>919</v>
@@ -14343,7 +14771,7 @@
         <v>927</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J114" s="1" t="s">
         <v>928</v>
@@ -14417,7 +14845,7 @@
         <v>934</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J115" s="1" t="s">
         <v>935</v>
@@ -14491,7 +14919,7 @@
         <v>856</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J116" s="1" t="s">
         <v>854</v>
@@ -14565,7 +14993,7 @@
         <v>944</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J117" s="1" t="s">
         <v>945</v>
@@ -14639,7 +15067,7 @@
         <v>951</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J118" s="1" t="s">
         <v>952</v>
@@ -14713,7 +15141,7 @@
         <v>959</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J119" s="1" t="s">
         <v>960</v>
@@ -14787,7 +15215,7 @@
         <v>966</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J120" s="1" t="s">
         <v>967</v>
@@ -14861,7 +15289,7 @@
         <v>973</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J121" s="1" t="s">
         <v>974</v>
@@ -14935,7 +15363,7 @@
         <v>981</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J122" s="1" t="s">
         <v>982</v>
@@ -15009,7 +15437,7 @@
         <v>989</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J123" s="1" t="s">
         <v>990</v>
@@ -15083,7 +15511,7 @@
         <v>998</v>
       </c>
       <c r="I124" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J124" s="1" t="s">
         <v>999</v>
@@ -15157,7 +15585,7 @@
         <v>1006</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J125" s="1" t="s">
         <v>1007</v>
@@ -15231,7 +15659,7 @@
         <v>1013</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J126" s="1" t="s">
         <v>1014</v>
@@ -15305,7 +15733,7 @@
         <v>1021</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J127" s="1" t="s">
         <v>1022</v>
@@ -15379,7 +15807,7 @@
         <v>1028</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J128" s="1" t="s">
         <v>1029</v>
@@ -15453,7 +15881,7 @@
         <v>1036</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J129" s="1" t="s">
         <v>1037</v>
@@ -15527,7 +15955,7 @@
         <v>1045</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J130" s="1" t="s">
         <v>1046</v>
@@ -15601,7 +16029,7 @@
         <v>1054</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J131" s="1" t="s">
         <v>1055</v>
@@ -15675,7 +16103,7 @@
         <v>1062</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J132" s="1" t="s">
         <v>1063</v>
@@ -15749,7 +16177,7 @@
         <v>1069</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J133" s="1" t="s">
         <v>1070</v>
@@ -15823,7 +16251,7 @@
         <v>1077</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J134" s="1" t="s">
         <v>1078</v>
@@ -15897,7 +16325,7 @@
         <v>1084</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J135" s="1" t="s">
         <v>1085</v>
@@ -15971,7 +16399,7 @@
         <v>1092</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J136" s="1" t="s">
         <v>1093</v>
@@ -16045,7 +16473,7 @@
         <v>1100</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J137" s="1" t="s">
         <v>1101</v>
@@ -16119,7 +16547,7 @@
         <v>1108</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J138" s="1" t="s">
         <v>1109</v>
@@ -16193,7 +16621,7 @@
         <v>729</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J139" s="1" t="s">
         <v>1116</v>
@@ -16267,7 +16695,7 @@
         <v>1121</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J140" s="1" t="s">
         <v>1122</v>
@@ -16341,7 +16769,7 @@
         <v>1129</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J141" s="1" t="s">
         <v>1130</v>
@@ -16415,7 +16843,7 @@
         <v>1136</v>
       </c>
       <c r="I142" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J142" s="1" t="s">
         <v>1137</v>
@@ -16489,7 +16917,7 @@
         <v>1142</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J143" s="1" t="s">
         <v>1143</v>
@@ -16563,7 +16991,7 @@
         <v>1150</v>
       </c>
       <c r="I144" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J144" s="1" t="s">
         <v>1151</v>
@@ -16637,7 +17065,7 @@
         <v>1157</v>
       </c>
       <c r="I145" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J145" s="1" t="s">
         <v>1158</v>
@@ -16711,7 +17139,7 @@
         <v>1165</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J146" s="1" t="s">
         <v>1166</v>
@@ -16785,7 +17213,7 @@
         <v>1173</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J147" s="1" t="s">
         <v>1174</v>
@@ -16859,7 +17287,7 @@
         <v>1180</v>
       </c>
       <c r="I148" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J148" s="1" t="s">
         <v>1181</v>
@@ -16933,7 +17361,7 @@
         <v>1187</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J149" s="1" t="s">
         <v>1188</v>
@@ -17007,7 +17435,7 @@
         <v>1194</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J150" s="1" t="s">
         <v>1195</v>
@@ -17081,7 +17509,7 @@
         <v>1201</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J151" s="1" t="s">
         <v>1202</v>
@@ -17155,7 +17583,7 @@
         <v>1209</v>
       </c>
       <c r="I152" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J152" s="1" t="s">
         <v>1210</v>
@@ -17229,7 +17657,7 @@
         <v>1216</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J153" s="1" t="s">
         <v>1217</v>
@@ -17303,7 +17731,7 @@
         <v>1223</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J154" s="1" t="s">
         <v>1224</v>
@@ -17377,7 +17805,7 @@
         <v>1232</v>
       </c>
       <c r="I155" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J155" s="1" t="s">
         <v>1233</v>
@@ -17451,7 +17879,7 @@
         <v>1239</v>
       </c>
       <c r="I156" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J156" s="1" t="s">
         <v>1240</v>
@@ -17525,7 +17953,7 @@
         <v>1246</v>
       </c>
       <c r="I157" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J157" s="1" t="s">
         <v>1247</v>
@@ -17599,7 +18027,7 @@
         <v>1253</v>
       </c>
       <c r="I158" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J158" s="1" t="s">
         <v>1254</v>
@@ -17673,7 +18101,7 @@
         <v>1261</v>
       </c>
       <c r="I159" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J159" s="1" t="s">
         <v>1262</v>
@@ -17747,7 +18175,7 @@
         <v>1269</v>
       </c>
       <c r="I160" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J160" s="1" t="s">
         <v>1270</v>
@@ -17821,7 +18249,7 @@
         <v>1276</v>
       </c>
       <c r="I161" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J161" s="1" t="s">
         <v>1277</v>
@@ -17895,7 +18323,7 @@
         <v>1283</v>
       </c>
       <c r="I162" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J162" s="1" t="s">
         <v>1284</v>
@@ -17969,7 +18397,7 @@
         <v>534</v>
       </c>
       <c r="I163" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J163" s="1" t="s">
         <v>1292</v>
@@ -18043,7 +18471,7 @@
         <v>1299</v>
       </c>
       <c r="I164" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J164" s="1" t="s">
         <v>1300</v>
@@ -18117,7 +18545,7 @@
         <v>1307</v>
       </c>
       <c r="I165" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J165" s="1" t="s">
         <v>1308</v>
@@ -18191,7 +18619,7 @@
         <v>1315</v>
       </c>
       <c r="I166" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J166" s="1" t="s">
         <v>1316</v>
@@ -18265,7 +18693,7 @@
         <v>1323</v>
       </c>
       <c r="I167" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J167" s="1" t="s">
         <v>1324</v>
@@ -18339,7 +18767,7 @@
         <v>1332</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>1821</v>
+        <v>1963</v>
       </c>
       <c r="J168" s="1" t="s">
         <v>1333</v>
@@ -18413,7 +18841,7 @@
         <v>1340</v>
       </c>
       <c r="I169" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J169" s="1" t="s">
         <v>1341</v>
@@ -18487,7 +18915,7 @@
         <v>405</v>
       </c>
       <c r="I170" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J170" s="1" t="s">
         <v>1346</v>
@@ -18561,7 +18989,7 @@
         <v>1351</v>
       </c>
       <c r="I171" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J171" s="1" t="s">
         <v>1352</v>
@@ -18635,7 +19063,7 @@
         <v>1359</v>
       </c>
       <c r="I172" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J172" s="1" t="s">
         <v>1360</v>
@@ -18709,7 +19137,7 @@
         <v>1366</v>
       </c>
       <c r="I173" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J173" s="1" t="s">
         <v>1367</v>
@@ -18783,7 +19211,7 @@
         <v>1373</v>
       </c>
       <c r="I174" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J174" s="1" t="s">
         <v>1374</v>
@@ -18857,7 +19285,7 @@
         <v>1380</v>
       </c>
       <c r="I175" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J175" s="1" t="s">
         <v>1381</v>
@@ -18931,7 +19359,7 @@
         <v>1387</v>
       </c>
       <c r="I176" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J176" s="1" t="s">
         <v>1388</v>
@@ -19005,7 +19433,7 @@
         <v>1394</v>
       </c>
       <c r="I177" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J177" s="1" t="s">
         <v>1395</v>
@@ -19079,7 +19507,7 @@
         <v>1401</v>
       </c>
       <c r="I178" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J178" s="1" t="s">
         <v>1402</v>
@@ -19153,7 +19581,7 @@
         <v>1408</v>
       </c>
       <c r="I179" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J179" s="1" t="s">
         <v>1409</v>
@@ -19227,7 +19655,7 @@
         <v>1415</v>
       </c>
       <c r="I180" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J180" s="1" t="s">
         <v>1416</v>
@@ -19301,7 +19729,7 @@
         <v>1421</v>
       </c>
       <c r="I181" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J181" s="1" t="s">
         <v>1422</v>
@@ -19375,7 +19803,7 @@
         <v>1428</v>
       </c>
       <c r="I182" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J182" s="1" t="s">
         <v>1429</v>
@@ -19449,7 +19877,7 @@
         <v>1435</v>
       </c>
       <c r="I183" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J183" s="1" t="s">
         <v>1436</v>
@@ -19523,7 +19951,7 @@
         <v>1443</v>
       </c>
       <c r="I184" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J184" s="1" t="s">
         <v>1444</v>
@@ -19597,7 +20025,7 @@
         <v>1450</v>
       </c>
       <c r="I185" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J185" s="1" t="s">
         <v>1451</v>
@@ -19671,7 +20099,7 @@
         <v>1457</v>
       </c>
       <c r="I186" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J186" s="1" t="s">
         <v>1458</v>
@@ -19745,7 +20173,7 @@
         <v>1464</v>
       </c>
       <c r="I187" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J187" s="1" t="s">
         <v>1465</v>
@@ -19819,7 +20247,7 @@
         <v>1472</v>
       </c>
       <c r="I188" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J188" s="1" t="s">
         <v>1473</v>
@@ -19893,7 +20321,7 @@
         <v>1479</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J189" s="1" t="s">
         <v>1480</v>
@@ -19967,7 +20395,7 @@
         <v>1486</v>
       </c>
       <c r="I190" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J190" s="1" t="s">
         <v>1487</v>
@@ -20041,7 +20469,7 @@
         <v>1494</v>
       </c>
       <c r="I191" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J191" s="1" t="s">
         <v>1495</v>
@@ -20115,7 +20543,7 @@
         <v>1502</v>
       </c>
       <c r="I192" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J192" s="1" t="s">
         <v>1503</v>
@@ -20189,7 +20617,7 @@
         <v>1510</v>
       </c>
       <c r="I193" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J193" s="1" t="s">
         <v>1511</v>
@@ -20263,7 +20691,7 @@
         <v>1518</v>
       </c>
       <c r="I194" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J194" s="1" t="s">
         <v>1519</v>
@@ -20337,7 +20765,7 @@
         <v>1525</v>
       </c>
       <c r="I195" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J195" s="1" t="s">
         <v>1526</v>
@@ -20411,7 +20839,7 @@
         <v>1533</v>
       </c>
       <c r="I196" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J196" s="1" t="s">
         <v>1534</v>
@@ -20485,7 +20913,7 @@
         <v>1541</v>
       </c>
       <c r="I197" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J197" s="1" t="s">
         <v>1542</v>
@@ -20559,7 +20987,7 @@
         <v>1548</v>
       </c>
       <c r="I198" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>1549</v>
@@ -20633,7 +21061,7 @@
         <v>1555</v>
       </c>
       <c r="I199" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>1556</v>
@@ -20707,7 +21135,7 @@
         <v>1561</v>
       </c>
       <c r="I200" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>1562</v>
@@ -20781,7 +21209,7 @@
         <v>1567</v>
       </c>
       <c r="I201" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>1568</v>
@@ -20855,7 +21283,7 @@
         <v>1574</v>
       </c>
       <c r="I202" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>1575</v>
@@ -20929,7 +21357,7 @@
         <v>1580</v>
       </c>
       <c r="I203" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>1581</v>
@@ -21003,7 +21431,7 @@
         <v>1587</v>
       </c>
       <c r="I204" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J204" s="1" t="s">
         <v>1588</v>
@@ -21077,7 +21505,7 @@
         <v>1595</v>
       </c>
       <c r="I205" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J205" s="1" t="s">
         <v>1596</v>
@@ -21151,7 +21579,7 @@
         <v>1602</v>
       </c>
       <c r="I206" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>1603</v>
@@ -21225,7 +21653,7 @@
         <v>1609</v>
       </c>
       <c r="I207" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>1610</v>
@@ -21299,7 +21727,7 @@
         <v>1617</v>
       </c>
       <c r="I208" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>1618</v>
@@ -21373,7 +21801,7 @@
         <v>1624</v>
       </c>
       <c r="I209" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>1625</v>
@@ -21447,7 +21875,7 @@
         <v>1631</v>
       </c>
       <c r="I210" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>1632</v>
@@ -21521,7 +21949,7 @@
         <v>1638</v>
       </c>
       <c r="I211" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>1639</v>
@@ -21595,7 +22023,7 @@
         <v>1645</v>
       </c>
       <c r="I212" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J212" s="1" t="s">
         <v>1646</v>
@@ -21669,7 +22097,7 @@
         <v>1653</v>
       </c>
       <c r="I213" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>1654</v>
@@ -21743,7 +22171,7 @@
         <v>1660</v>
       </c>
       <c r="I214" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J214" s="1" t="s">
         <v>1661</v>
@@ -21817,7 +22245,7 @@
         <v>1668</v>
       </c>
       <c r="I215" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>1669</v>
@@ -21891,7 +22319,7 @@
         <v>1676</v>
       </c>
       <c r="I216" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>1677</v>
@@ -21965,7 +22393,7 @@
         <v>1683</v>
       </c>
       <c r="I217" s="4" t="s">
-        <v>1820</v>
+        <v>1962</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>1684</v>
@@ -22039,7 +22467,7 @@
         <v>1690</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J218" s="1" t="s">
         <v>1691</v>
@@ -22113,7 +22541,7 @@
         <v>1697</v>
       </c>
       <c r="I219" s="4" t="s">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="J219" s="1" t="s">
         <v>1698</v>
@@ -22187,7 +22615,7 @@
         <v>1723</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J220" s="1" t="s">
         <v>1724</v>
@@ -22261,7 +22689,7 @@
         <v>1731</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>1732</v>
@@ -22329,7 +22757,7 @@
         <v>1737</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>1738</v>
@@ -22379,7 +22807,7 @@
         <v>1744</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>1745</v>
@@ -22429,7 +22857,7 @@
         <v>1752</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J224" s="1" t="s">
         <v>1753</v>
@@ -22479,7 +22907,7 @@
         <v>1758</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J225" s="1" t="s">
         <v>1759</v>
@@ -22529,7 +22957,7 @@
         <v>1766</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J226" s="1" t="s">
         <v>1767</v>
@@ -22579,7 +23007,7 @@
         <v>1774</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J227" s="1" t="s">
         <v>1775</v>
@@ -22629,7 +23057,7 @@
         <v>1783</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>1784</v>
@@ -22679,7 +23107,7 @@
         <v>1791</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>1792</v>
@@ -22729,7 +23157,7 @@
         <v>1800</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J230" s="1" t="s">
         <v>1801</v>
@@ -22779,7 +23207,7 @@
         <v>1807</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J231" s="1" t="s">
         <v>1808</v>
@@ -22829,7 +23257,7 @@
         <v>1813</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>1822</v>
+        <v>1964</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>1814</v>
@@ -22865,6 +23293,956 @@
         <v>94</v>
       </c>
       <c r="U232" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="233" spans="6:21">
+      <c r="F233" s="1" t="s">
+        <v>1820</v>
+      </c>
+      <c r="G233" s="1">
+        <v>231</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="K233" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="L233" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M233" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N233" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="O233" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="P233" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="Q233" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R233" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="S233" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T233" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U233" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="234" spans="6:21">
+      <c r="F234" s="1" t="s">
+        <v>1827</v>
+      </c>
+      <c r="G234" s="1">
+        <v>232</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>1828</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J234" s="1" t="s">
+        <v>1829</v>
+      </c>
+      <c r="K234" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="L234" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M234" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N234" s="1" t="s">
+        <v>1831</v>
+      </c>
+      <c r="O234" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="P234" s="1" t="s">
+        <v>1833</v>
+      </c>
+      <c r="Q234" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R234" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="S234" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T234" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U234" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="235" spans="6:21">
+      <c r="F235" s="1" t="s">
+        <v>1834</v>
+      </c>
+      <c r="G235" s="1">
+        <v>233</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J235" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="K235" s="1" t="s">
+        <v>1837</v>
+      </c>
+      <c r="L235" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M235" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N235" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="O235" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="P235" s="1" t="s">
+        <v>1840</v>
+      </c>
+      <c r="Q235" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R235" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="S235" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T235" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U235" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="236" spans="6:21">
+      <c r="F236" s="1" t="s">
+        <v>1842</v>
+      </c>
+      <c r="G236" s="1">
+        <v>234</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>1843</v>
+      </c>
+      <c r="I236" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J236" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="K236" s="1" t="s">
+        <v>1845</v>
+      </c>
+      <c r="L236" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M236" s="1" t="s">
+        <v>1846</v>
+      </c>
+      <c r="N236" s="1" t="s">
+        <v>1847</v>
+      </c>
+      <c r="O236" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="P236" s="1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="Q236" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="R236" s="1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="S236" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T236" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U236" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="237" spans="6:21">
+      <c r="F237" s="1" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G237" s="1">
+        <v>235</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>1852</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J237" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="K237" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="L237" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M237" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N237" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="O237" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="P237" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="Q237" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="R237" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="S237" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T237" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="U237" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="238" spans="6:21">
+      <c r="F238" s="1" t="s">
+        <v>1859</v>
+      </c>
+      <c r="G238" s="1">
+        <v>236</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>1860</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J238" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="K238" s="1" t="s">
+        <v>1862</v>
+      </c>
+      <c r="L238" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M238" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="N238" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="O238" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="P238" s="1" t="s">
+        <v>1866</v>
+      </c>
+      <c r="Q238" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R238" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="S238" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T238" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U238" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="239" spans="6:21">
+      <c r="F239" s="1" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G239" s="1">
+        <v>237</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>1869</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J239" s="1" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K239" s="1" t="s">
+        <v>1871</v>
+      </c>
+      <c r="L239" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M239" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N239" s="1" t="s">
+        <v>1872</v>
+      </c>
+      <c r="O239" s="1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="P239" s="1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="Q239" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R239" s="1" t="s">
+        <v>1875</v>
+      </c>
+      <c r="S239" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T239" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U239" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="240" spans="6:21">
+      <c r="F240" s="1" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G240" s="1">
+        <v>238</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="K240" s="1" t="s">
+        <v>1879</v>
+      </c>
+      <c r="L240" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M240" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N240" s="1" t="s">
+        <v>1880</v>
+      </c>
+      <c r="O240" s="1" t="s">
+        <v>1881</v>
+      </c>
+      <c r="P240" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="Q240" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R240" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="S240" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T240" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U240" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="241" spans="6:21">
+      <c r="F241" s="1" t="s">
+        <v>1883</v>
+      </c>
+      <c r="G241" s="1">
+        <v>239</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>1884</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J241" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="K241" s="1" t="s">
+        <v>1886</v>
+      </c>
+      <c r="L241" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M241" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="N241" s="1" t="s">
+        <v>1887</v>
+      </c>
+      <c r="O241" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="P241" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="Q241" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="R241" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="S241" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T241" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U241" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="242" spans="6:21">
+      <c r="F242" s="1" t="s">
+        <v>1890</v>
+      </c>
+      <c r="G242" s="1">
+        <v>240</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J242" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K242" s="1" t="s">
+        <v>1893</v>
+      </c>
+      <c r="L242" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M242" s="1" t="s">
+        <v>1894</v>
+      </c>
+      <c r="N242" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="O242" s="1" t="s">
+        <v>1896</v>
+      </c>
+      <c r="P242" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="Q242" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R242" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="S242" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T242" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="U242" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="243" spans="6:21">
+      <c r="F243" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G243" s="1">
+        <v>241</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J243" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="K243" s="1" t="s">
+        <v>1900</v>
+      </c>
+      <c r="L243" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M243" s="1" t="s">
+        <v>1894</v>
+      </c>
+      <c r="N243" s="1" t="s">
+        <v>1901</v>
+      </c>
+      <c r="O243" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="P243" s="1" t="s">
+        <v>1902</v>
+      </c>
+      <c r="Q243" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R243" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="S243" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T243" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U243" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="244" spans="6:21">
+      <c r="F244" s="1" t="s">
+        <v>1903</v>
+      </c>
+      <c r="G244" s="1">
+        <v>242</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>1904</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J244" s="1" t="s">
+        <v>1905</v>
+      </c>
+      <c r="K244" s="1" t="s">
+        <v>1906</v>
+      </c>
+      <c r="L244" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M244" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N244" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="O244" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="P244" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="Q244" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="R244" s="1" t="s">
+        <v>1910</v>
+      </c>
+      <c r="S244" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T244" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U244" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="245" spans="6:21">
+      <c r="F245" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G245" s="1">
+        <v>243</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>1912</v>
+      </c>
+      <c r="I245" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J245" s="1" t="s">
+        <v>1913</v>
+      </c>
+      <c r="K245" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="L245" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M245" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N245" s="1" t="s">
+        <v>1915</v>
+      </c>
+      <c r="O245" s="1" t="s">
+        <v>1916</v>
+      </c>
+      <c r="P245" s="1" t="s">
+        <v>1917</v>
+      </c>
+      <c r="Q245" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R245" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="S245" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="T245" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="U245" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="246" spans="6:21">
+      <c r="F246" s="1" t="s">
+        <v>1920</v>
+      </c>
+      <c r="G246" s="1">
+        <v>244</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="I246" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J246" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="K246" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="L246" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M246" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="N246" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="O246" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="P246" s="1" t="s">
+        <v>1925</v>
+      </c>
+      <c r="Q246" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="R246" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="S246" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T246" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="U246" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="247" spans="6:21">
+      <c r="F247" s="1" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G247" s="1">
+        <v>245</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>1927</v>
+      </c>
+      <c r="I247" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="K247" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L247" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M247" s="1" t="s">
+        <v>1929</v>
+      </c>
+      <c r="N247" s="1" t="s">
+        <v>1930</v>
+      </c>
+      <c r="O247" s="1" t="s">
+        <v>1931</v>
+      </c>
+      <c r="P247" s="1" t="s">
+        <v>1932</v>
+      </c>
+      <c r="Q247" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R247" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S247" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T247" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="U247" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="248" spans="6:21">
+      <c r="F248" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G248" s="1">
+        <v>246</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>1934</v>
+      </c>
+      <c r="I248" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J248" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="K248" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="L248" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M248" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="N248" s="1" t="s">
+        <v>1938</v>
+      </c>
+      <c r="O248" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="P248" s="1" t="s">
+        <v>1940</v>
+      </c>
+      <c r="Q248" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R248" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="S248" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T248" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U248" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="249" spans="6:21">
+      <c r="F249" s="1" t="s">
+        <v>1941</v>
+      </c>
+      <c r="G249" s="1">
+        <v>247</v>
+      </c>
+      <c r="H249" s="1" t="s">
+        <v>1942</v>
+      </c>
+      <c r="I249" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J249" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="K249" s="1" t="s">
+        <v>1944</v>
+      </c>
+      <c r="L249" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M249" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N249" s="1" t="s">
+        <v>1945</v>
+      </c>
+      <c r="O249" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="P249" s="1" t="s">
+        <v>1947</v>
+      </c>
+      <c r="Q249" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R249" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="S249" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T249" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U249" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="250" spans="6:21">
+      <c r="F250" s="1" t="s">
+        <v>1948</v>
+      </c>
+      <c r="G250" s="1">
+        <v>248</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J250" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="K250" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L250" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M250" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N250" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="O250" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="P250" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="Q250" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R250" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="S250" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T250" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U250" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="251" spans="6:21">
+      <c r="F251" s="1" t="s">
+        <v>1954</v>
+      </c>
+      <c r="G251" s="1">
+        <v>249</v>
+      </c>
+      <c r="H251" s="1" t="s">
+        <v>1955</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J251" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="K251" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="L251" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M251" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N251" s="1" t="s">
+        <v>1958</v>
+      </c>
+      <c r="O251" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="P251" s="1" t="s">
+        <v>1960</v>
+      </c>
+      <c r="Q251" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R251" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="S251" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T251" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U251" s="1" t="s">
         <v>72</v>
       </c>
     </row>
@@ -22873,7 +24251,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="L2:U2 A1:J2 V1:AG221 A3:E221 L1:P1 R1:U1" numberStoredAsText="1"/>
+    <ignoredError sqref="L2:U2 A1:J2 V1:AG221 L1:P1 R1:U1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
